--- a/output/pdf_financials_xlsx/BAD.xlsx
+++ b/output/pdf_financials_xlsx/BAD.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.661846</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.3332</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.3332</v>
       </c>
     </row>
     <row r="93">
@@ -3139,7 +3139,11 @@
           <t>Share-based payment reserve (note 5)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3501,7 +3505,11 @@
           <t>Warrants reserve (note 6)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>4.328646</v>
       </c>
@@ -3528,7 +3536,11 @@
           <t>Share-based payment reserve (note 6)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>1.3332</v>
       </c>

--- a/output/pdf_financials_xlsx/BAD.xlsx
+++ b/output/pdf_financials_xlsx/BAD.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.051599</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003225</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.002993</v>
@@ -867,10 +867,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.25575</v>
+        <v>-2.307349</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.144071</v>
+        <v>-8.147296000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>5.31118</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.25575</v>
+        <v>-2.307349</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.144071</v>
+        <v>-8.147296000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>5.31118</v>
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017577</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01904</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.567547</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017577</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.01904</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.567547</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.424411</v>
+        <v>0.406834</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>6.542878</v>
+        <v>6.523838</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.304929</v>
+        <v>7.737382</v>
       </c>
     </row>
     <row r="49">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">

--- a/output/pdf_financials_xlsx/BAD.xlsx
+++ b/output/pdf_financials_xlsx/BAD.xlsx
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.501507</v>
       </c>
     </row>
     <row r="116">
@@ -4160,7 +4160,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
